--- a/강의예제/7장_기본과_필수_함수_익히기/7장_복습.xlsx
+++ b/강의예제/7장_기본과_필수_함수_익히기/7장_복습.xlsx
@@ -1285,9 +1285,10 @@
           <t>SUMIFS 만 쓰면 안 헷갈립니다</t>
         </is>
       </c>
-      <c r="D6" s="16">
-        <f>SUMIFS($D$5:$D$10,$B$5:$B$10,"서울") → 260,600 / 조건 둘 → 177,900 / =SUMIFS($D$5:$D$10,$D$5:$D$10,"&gt;=100000") → 1,246,600</f>
-        <v/>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>=SUMIFS($D$5:$D$10,$B$5:$B$10,"서울") → 260,600 / 조건 둘 → 177,900 / =SUMIFS($D$5:$D$10,$D$5:$D$10,"&gt;=100000") → 1,246,600</t>
+        </is>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
